--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9024390243902439</v>
+        <v>0.9080459770114943</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7183098591549296</v>
+        <v>0.7253521126760564</v>
       </c>
       <c r="D2">
-        <v>0.3508771929824561</v>
+        <v>0.3305084745762712</v>
       </c>
       <c r="E2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
